--- a/Data_Cleaning.xlsx
+++ b/Data_Cleaning.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2643" uniqueCount="639">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2642" uniqueCount="638">
   <si>
     <t>Order_ID</t>
   </si>
@@ -1500,9 +1500,6 @@
   </si>
   <si>
     <t>9403761379</t>
-  </si>
-  <si>
-    <t>f</t>
   </si>
   <si>
     <t>Issue Found</t>
@@ -14688,9 +14685,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="18" t="s">
-        <v>494</v>
-      </c>
+      <c r="A48" s="18"/>
       <c r="B48" s="15" t="s">
         <v>144</v>
       </c>
@@ -14760,262 +14755,262 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="s">
+        <v>494</v>
+      </c>
+      <c r="B1" s="23" t="s">
         <v>495</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="C1" s="23" t="s">
         <v>496</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="D1" s="23" t="s">
         <v>497</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="E1" s="23" t="s">
         <v>498</v>
       </c>
-      <c r="E1" s="23" t="s">
+      <c r="F1" s="23" t="s">
         <v>499</v>
-      </c>
-      <c r="F1" s="23" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="22" t="s">
+        <v>500</v>
+      </c>
+      <c r="B2" s="22" t="s">
         <v>501</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="C2" s="22" t="s">
         <v>502</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="D2" s="22" t="s">
         <v>503</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="E2" s="22" t="s">
         <v>504</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="F2" s="22" t="s">
         <v>505</v>
-      </c>
-      <c r="F2" s="22" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="22" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B3" s="22" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="22" t="s">
+        <v>507</v>
+      </c>
+      <c r="D3" s="22" t="s">
         <v>508</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="E3" s="22" t="s">
         <v>509</v>
       </c>
-      <c r="E3" s="22" t="s">
-        <v>510</v>
-      </c>
       <c r="F3" s="22" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="22" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B4" s="22" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="22" t="s">
+        <v>511</v>
+      </c>
+      <c r="D4" s="22" t="s">
         <v>512</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="E4" s="22" t="s">
         <v>513</v>
       </c>
-      <c r="E4" s="22" t="s">
-        <v>514</v>
-      </c>
       <c r="F4" s="22" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="22" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B5" s="22" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="22" t="s">
+        <v>515</v>
+      </c>
+      <c r="D5" s="22" t="s">
         <v>516</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="E5" s="22" t="s">
         <v>517</v>
       </c>
-      <c r="E5" s="22" t="s">
-        <v>518</v>
-      </c>
       <c r="F5" s="22" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="22" t="s">
+        <v>518</v>
+      </c>
+      <c r="B6" s="22" t="s">
         <v>519</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="C6" s="22" t="s">
         <v>520</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="D6" s="22" t="s">
         <v>521</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="E6" s="22" t="s">
         <v>522</v>
       </c>
-      <c r="E6" s="22" t="s">
-        <v>523</v>
-      </c>
       <c r="F6" s="22" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="22" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B7" s="22" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="22" t="s">
+        <v>524</v>
+      </c>
+      <c r="D7" s="22" t="s">
         <v>525</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="E7" s="22" t="s">
         <v>526</v>
       </c>
-      <c r="E7" s="22" t="s">
-        <v>527</v>
-      </c>
       <c r="F7" s="22" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="22" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B8" s="22" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D8" s="22" t="s">
+        <v>528</v>
+      </c>
+      <c r="E8" s="22" t="s">
         <v>529</v>
       </c>
-      <c r="E8" s="22" t="s">
-        <v>530</v>
-      </c>
       <c r="F8" s="22" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="22" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B9" s="22" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="22" t="s">
+        <v>531</v>
+      </c>
+      <c r="D9" s="22" t="s">
         <v>532</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="E9" s="22" t="s">
         <v>533</v>
       </c>
-      <c r="E9" s="22" t="s">
-        <v>534</v>
-      </c>
       <c r="F9" s="22" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="22" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B10" s="22" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="22" t="s">
+        <v>535</v>
+      </c>
+      <c r="D10" s="22" t="s">
         <v>536</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="E10" s="22" t="s">
         <v>537</v>
       </c>
-      <c r="E10" s="22" t="s">
-        <v>538</v>
-      </c>
       <c r="F10" s="22" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="22" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B11" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D11" s="22" t="s">
+        <v>539</v>
+      </c>
+      <c r="E11" s="22" t="s">
         <v>540</v>
       </c>
-      <c r="E11" s="22" t="s">
-        <v>541</v>
-      </c>
       <c r="F11" s="22" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="22" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B12" s="22" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D12" s="22" t="s">
+        <v>542</v>
+      </c>
+      <c r="E12" s="22" t="s">
         <v>543</v>
       </c>
-      <c r="E12" s="22" t="s">
-        <v>544</v>
-      </c>
       <c r="F12" s="22" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="22" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B13" s="22" t="s">
         <v>13</v>
       </c>
       <c r="C13" s="22" t="s">
+        <v>545</v>
+      </c>
+      <c r="D13" s="22" t="s">
         <v>546</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="E13" s="22" t="s">
         <v>547</v>
       </c>
-      <c r="E13" s="22" t="s">
-        <v>548</v>
-      </c>
       <c r="F13" s="22" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -16031,19 +16026,19 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="s">
+        <v>548</v>
+      </c>
+      <c r="B1" s="23" t="s">
         <v>549</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="C1" s="23" t="s">
         <v>550</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="D1" s="23" t="s">
         <v>551</v>
       </c>
-      <c r="D1" s="23" t="s">
-        <v>552</v>
-      </c>
       <c r="E1" s="24" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="2">
@@ -16051,16 +16046,16 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="22" t="s">
+        <v>552</v>
+      </c>
+      <c r="C2" s="22" t="s">
         <v>553</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="D2" s="22" t="s">
         <v>554</v>
       </c>
-      <c r="D2" s="22" t="s">
-        <v>555</v>
-      </c>
       <c r="E2" s="18" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="3">
@@ -16068,16 +16063,16 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="22" t="s">
+        <v>555</v>
+      </c>
+      <c r="C3" s="22" t="s">
         <v>556</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="D3" s="22" t="s">
         <v>557</v>
       </c>
-      <c r="D3" s="22" t="s">
-        <v>558</v>
-      </c>
       <c r="E3" s="22" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="4">
@@ -16085,16 +16080,16 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="22" t="s">
+        <v>558</v>
+      </c>
+      <c r="C4" s="22" t="s">
         <v>559</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="D4" s="22" t="s">
         <v>560</v>
       </c>
-      <c r="D4" s="22" t="s">
-        <v>561</v>
-      </c>
       <c r="E4" s="18" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="5">
@@ -16102,16 +16097,16 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="22" t="s">
+        <v>561</v>
+      </c>
+      <c r="C5" s="22" t="s">
         <v>562</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="D5" s="22" t="s">
         <v>563</v>
       </c>
-      <c r="D5" s="22" t="s">
-        <v>564</v>
-      </c>
       <c r="E5" s="22" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="6">
@@ -16119,16 +16114,16 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="22" t="s">
+        <v>564</v>
+      </c>
+      <c r="C6" s="22" t="s">
         <v>565</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="D6" s="22" t="s">
         <v>566</v>
       </c>
-      <c r="D6" s="22" t="s">
-        <v>567</v>
-      </c>
       <c r="E6" s="18" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="7">
@@ -16136,16 +16131,16 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="22" t="s">
+        <v>567</v>
+      </c>
+      <c r="C7" s="22" t="s">
         <v>568</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="D7" s="22" t="s">
         <v>569</v>
       </c>
-      <c r="D7" s="22" t="s">
-        <v>570</v>
-      </c>
       <c r="E7" s="22" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="8">
@@ -16153,16 +16148,16 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="22" t="s">
+        <v>570</v>
+      </c>
+      <c r="C8" s="22" t="s">
         <v>571</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="D8" s="22" t="s">
         <v>572</v>
       </c>
-      <c r="D8" s="22" t="s">
-        <v>573</v>
-      </c>
       <c r="E8" s="18" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="9">
@@ -16170,16 +16165,16 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="22" t="s">
+        <v>573</v>
+      </c>
+      <c r="C9" s="22" t="s">
         <v>574</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="D9" s="22" t="s">
         <v>575</v>
       </c>
-      <c r="D9" s="22" t="s">
-        <v>576</v>
-      </c>
       <c r="E9" s="22" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="10">
@@ -16187,16 +16182,16 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="22" t="s">
+        <v>576</v>
+      </c>
+      <c r="C10" s="22" t="s">
         <v>577</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="D10" s="22" t="s">
         <v>578</v>
       </c>
-      <c r="D10" s="22" t="s">
-        <v>579</v>
-      </c>
       <c r="E10" s="18" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="11">
@@ -16204,16 +16199,16 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="22" t="s">
+        <v>579</v>
+      </c>
+      <c r="C11" s="22" t="s">
         <v>580</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="D11" s="22" t="s">
         <v>581</v>
       </c>
-      <c r="D11" s="22" t="s">
-        <v>582</v>
-      </c>
       <c r="E11" s="22" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="12">
@@ -16221,16 +16216,16 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="22" t="s">
+        <v>582</v>
+      </c>
+      <c r="C12" s="22" t="s">
         <v>583</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="D12" s="22" t="s">
         <v>584</v>
       </c>
-      <c r="D12" s="22" t="s">
-        <v>585</v>
-      </c>
       <c r="E12" s="18" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="13">
@@ -16238,16 +16233,16 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="22" t="s">
+        <v>585</v>
+      </c>
+      <c r="C13" s="22" t="s">
         <v>586</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="D13" s="22" t="s">
         <v>587</v>
       </c>
-      <c r="D13" s="22" t="s">
-        <v>588</v>
-      </c>
       <c r="E13" s="22" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="14">
@@ -16255,16 +16250,16 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="22" t="s">
+        <v>588</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>580</v>
+      </c>
+      <c r="D14" s="22" t="s">
         <v>589</v>
       </c>
-      <c r="C14" s="22" t="s">
-        <v>581</v>
-      </c>
-      <c r="D14" s="22" t="s">
-        <v>590</v>
-      </c>
       <c r="E14" s="18" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="15">
@@ -16272,16 +16267,16 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="22" t="s">
+        <v>590</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>580</v>
+      </c>
+      <c r="D15" s="22" t="s">
         <v>591</v>
       </c>
-      <c r="C15" s="22" t="s">
-        <v>581</v>
-      </c>
-      <c r="D15" s="22" t="s">
-        <v>592</v>
-      </c>
       <c r="E15" s="22" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="16">
@@ -16289,16 +16284,16 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="22" t="s">
+        <v>592</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>520</v>
+      </c>
+      <c r="D16" s="22" t="s">
         <v>593</v>
       </c>
-      <c r="C16" s="22" t="s">
-        <v>521</v>
-      </c>
-      <c r="D16" s="22" t="s">
-        <v>594</v>
-      </c>
       <c r="E16" s="18" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="17">
@@ -16306,16 +16301,16 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="22" t="s">
+        <v>594</v>
+      </c>
+      <c r="C17" s="22" t="s">
         <v>595</v>
       </c>
-      <c r="C17" s="22" t="s">
+      <c r="D17" s="22" t="s">
         <v>596</v>
       </c>
-      <c r="D17" s="22" t="s">
-        <v>597</v>
-      </c>
       <c r="E17" s="22" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -17334,19 +17329,19 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="s">
+        <v>597</v>
+      </c>
+      <c r="B1" s="23" t="s">
         <v>598</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="C1" s="23" t="s">
         <v>599</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="D1" s="24" t="s">
         <v>600</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="E1" s="24" t="s">
         <v>601</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>602</v>
       </c>
       <c r="F1" s="23"/>
       <c r="G1" s="23"/>
@@ -17356,13 +17351,13 @@
         <v>0</v>
       </c>
       <c r="B2" s="22" t="s">
+        <v>602</v>
+      </c>
+      <c r="C2" s="22" t="s">
         <v>603</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="D2" s="18" t="s">
         <v>604</v>
-      </c>
-      <c r="D2" s="18" t="s">
-        <v>605</v>
       </c>
       <c r="E2" s="25" t="s">
         <v>15</v>
@@ -17373,13 +17368,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="22" t="s">
+        <v>605</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>603</v>
+      </c>
+      <c r="D3" s="22" t="s">
         <v>606</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>604</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>607</v>
       </c>
       <c r="E3" s="26" t="s">
         <v>16</v>
@@ -17390,13 +17385,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="22" t="s">
+        <v>607</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>603</v>
+      </c>
+      <c r="D4" s="18" t="s">
         <v>608</v>
-      </c>
-      <c r="C4" s="22" t="s">
-        <v>604</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>609</v>
       </c>
       <c r="E4" s="25" t="s">
         <v>152</v>
@@ -17407,13 +17402,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="22" t="s">
+        <v>609</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>603</v>
+      </c>
+      <c r="D5" s="22" t="s">
         <v>610</v>
-      </c>
-      <c r="C5" s="22" t="s">
-        <v>604</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>611</v>
       </c>
       <c r="E5" s="26" t="s">
         <v>18</v>
@@ -17424,13 +17419,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="22" t="s">
+        <v>611</v>
+      </c>
+      <c r="C6" s="22" t="s">
         <v>612</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="D6" s="18" t="s">
         <v>613</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>614</v>
       </c>
       <c r="E6" s="25">
         <v>9.87654321E9</v>
@@ -17441,13 +17436,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="22" t="s">
+        <v>614</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>603</v>
+      </c>
+      <c r="D7" s="22" t="s">
         <v>615</v>
-      </c>
-      <c r="C7" s="22" t="s">
-        <v>604</v>
-      </c>
-      <c r="D7" s="22" t="s">
-        <v>616</v>
       </c>
       <c r="E7" s="26" t="s">
         <v>20</v>
@@ -17458,13 +17453,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="22" t="s">
+        <v>616</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>603</v>
+      </c>
+      <c r="D8" s="18" t="s">
         <v>617</v>
-      </c>
-      <c r="C8" s="22" t="s">
-        <v>604</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>618</v>
       </c>
       <c r="E8" s="25" t="s">
         <v>192</v>
@@ -17475,13 +17470,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="22" t="s">
+        <v>618</v>
+      </c>
+      <c r="C9" s="22" t="s">
         <v>619</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="D9" s="22" t="s">
         <v>620</v>
-      </c>
-      <c r="D9" s="22" t="s">
-        <v>621</v>
       </c>
       <c r="E9" s="27">
         <v>45293.0</v>
@@ -17493,13 +17488,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="22" t="s">
+        <v>621</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>603</v>
+      </c>
+      <c r="D10" s="18" t="s">
         <v>622</v>
-      </c>
-      <c r="C10" s="22" t="s">
-        <v>604</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>623</v>
       </c>
       <c r="E10" s="25" t="s">
         <v>22</v>
@@ -17510,13 +17505,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="22" t="s">
+        <v>623</v>
+      </c>
+      <c r="C11" s="22" t="s">
         <v>624</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="D11" s="22" t="s">
         <v>625</v>
-      </c>
-      <c r="D11" s="22" t="s">
-        <v>626</v>
       </c>
       <c r="E11" s="26">
         <v>3.0</v>
@@ -17527,13 +17522,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="22" t="s">
+        <v>626</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>624</v>
+      </c>
+      <c r="D12" s="18" t="s">
         <v>627</v>
-      </c>
-      <c r="C12" s="22" t="s">
-        <v>625</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>628</v>
       </c>
       <c r="E12" s="25">
         <v>2563.0</v>
@@ -17544,13 +17539,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="22" t="s">
+        <v>628</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>603</v>
+      </c>
+      <c r="D13" s="22" t="s">
         <v>629</v>
-      </c>
-      <c r="C13" s="22" t="s">
-        <v>604</v>
-      </c>
-      <c r="D13" s="22" t="s">
-        <v>630</v>
       </c>
       <c r="E13" s="26" t="s">
         <v>23</v>
@@ -17561,13 +17556,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="22" t="s">
+        <v>630</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>603</v>
+      </c>
+      <c r="D14" s="18" t="s">
         <v>631</v>
-      </c>
-      <c r="C14" s="22" t="s">
-        <v>604</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>632</v>
       </c>
       <c r="E14" s="25" t="s">
         <v>36</v>
@@ -17578,13 +17573,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="22" t="s">
+        <v>632</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>624</v>
+      </c>
+      <c r="D15" s="22" t="s">
         <v>633</v>
-      </c>
-      <c r="C15" s="22" t="s">
-        <v>625</v>
-      </c>
-      <c r="D15" s="22" t="s">
-        <v>634</v>
       </c>
       <c r="E15" s="26">
         <v>4.0</v>
@@ -17595,13 +17590,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="22" t="s">
+        <v>634</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>603</v>
+      </c>
+      <c r="D16" s="18" t="s">
         <v>635</v>
-      </c>
-      <c r="C16" s="22" t="s">
-        <v>604</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>636</v>
       </c>
       <c r="E16" s="25" t="s">
         <v>25</v>
@@ -17612,13 +17607,13 @@
         <v>483</v>
       </c>
       <c r="B17" s="22" t="s">
+        <v>636</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>624</v>
+      </c>
+      <c r="D17" s="22" t="s">
         <v>637</v>
-      </c>
-      <c r="C17" s="22" t="s">
-        <v>625</v>
-      </c>
-      <c r="D17" s="22" t="s">
-        <v>638</v>
       </c>
       <c r="E17" s="26">
         <v>7689.0</v>
